--- a/tools/find-a-venue/data/off_tech_tabs.xlsx
+++ b/tools/find-a-venue/data/off_tech_tabs.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Off Tech history" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Past events" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field guide" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18981,4 +18982,527 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Shown on site?</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Allowed values</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>What to enter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Venue ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>The venue's web address on the site. Leave blank for a new venue (the sync creates one), and never change it once set.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Approved · Pending review · Archived</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Only Approved venues appear on the site. New venues start as Pending review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Venue name</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Venue details</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Common name of the space.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Venue type</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Venue details</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Park / public space · Privately owned public space (POPS) · Library · Bar / cafe / restaurant · Club / event venue · Arts / community space · Gallery / museum · Bookstore · Church / meeting house · University · Makerspace · Community tech space · Radio station / studio · Other</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>What kind of place this is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Venue details</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Street address, or cross streets for a park. Public places only: never a private home.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Neighborhood</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Venue details</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Borough</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Venue details</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Manhattan · Brooklyn · Queens · Bronx · Staten Island</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Indoor / outdoor</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Venue details</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Indoor · Outdoor · Both</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Capacity (est.)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Venue details</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Rough number of people the space holds. An estimate is fine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Venue details</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Free · Donation · Purchase / minimum spend · Rental fee · Ticketed by venue · Unknown</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Shown as 'Public / cost'. Parks, plazas and libraries also show as public spaces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>How to book</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Venue notes</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Freeform. Who to ask, how far ahead, permits, any fees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Venue notes</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Freeform and PUBLIC: an events email, booking form or front desk. Never a personal email or phone; put those in Private notes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Food &amp; drink</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Venue notes</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Freeform. Outside food OK? Purchase required? Alcohol?</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Venue notes</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Freeform. Step-free entry, elevator, accessible restroom, seating, lighting, quiet corner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A/V equipment</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Venue notes</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Freeform. Power outlets, sound system or mic, projector or screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Other notes</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Venue notes</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Freeform. Anything else: where to set up, what's worked, what to avoid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Private notes</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Collaborators only</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Never published. Personal contacts (name, email, phone), who knows the venue, anything sensitive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Last verified</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Upkeep</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Date someone last confirmed these details (YYYY-MM-DD).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Upkeep</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Decimal degrees. Leave blank and the sync fills it in from the address.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Upkeep</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Decimal degrees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Copied from tools/find-a-venue/field_guide.csv, which the sync reads. Edit it there.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>